--- a/data/worldcup_0623_0622update.xlsx
+++ b/data/worldcup_0623_0622update.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阿根廷vs奥地利" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法国vs伊拉克" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法国vs伊拉克" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阿根廷vs奥地利" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挪威vs塞内加尔" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="约旦vs阿尔及利亚" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -458,115 +458,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Is Lionel Messi injured for Argentina vs Austria? World Cup star’s fitness latest</t>
+          <t>队报：法国vs伊拉克可能受雷暴天气影响，若不顺利恐怕要踢数小时</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>zhibo8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 09</t>
+          <t>2026-06-22 17:50:15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/person/player/is-lionel-messi-injured-for-argentina-vs-austria-world-cup-stars-fitness-latest</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lionel Messi has already caused a stir at World Cup 2026.  He needed just 76 minutes of this summer’s tournament to complete a hat-trick of finishes, </t>
-        </is>
-      </c>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a3901bd0f938native.htm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina vs Austria preview: World Cup Group J at AT&amp;T Stadium</t>
+          <t>队报预测法国vs伊拉克首发：姆总、奥利塞、登贝莱和巴尔科拉出战</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>zhibo8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-22T08:00:00</t>
+          <t>2026-06-22 17:50:15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/argentina-vs-austria-preview-world-cup-group-j-at-att-stadium</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Argentina face Austria in World Cup Group J at AT&amp;T Stadium. We break down form, trends, projected lineups, odds, and the key Sofascore Rating leaders</t>
-        </is>
-      </c>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a3900c8421e4native.htm</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scaloni and Argentina prepare for Austria</t>
+          <t>伊拉克主帅：能和法国队交手是荣幸，也是我们展现实力的机会</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>dongqiudi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-22T03:20:34</t>
+          <t>2026-06-22 06:53</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49140889/scaloni-argentina-prepare-austria</t>
+          <t>https://www.dongqiudi.com/article/5956272</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lizzy Becherano analyzes Argentina's upcoming match against Austria in Dallas.</t>
+          <t>伊拉克将在世界杯小组赛第二场对阵法国，主帅阿诺德赛前接受了拜因体育的采访。
+对伊拉克队来说，这是一段非常美妙的经历。能够与法国队这样的球队交手，是一种荣幸。我之前也公开表示过，我非常享受这一切。无论是对阵挪威，还是接下来的比赛，都是如此。我从中收获了很多快乐。
+会的。为了争取最好的结果，我们必须</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Austria's Stefan Posch will play vs. Argentina despite broken jaw</t>
+          <t>法媒：楚阿梅尼缺席法国战伊拉克前最后一练，预计不会首发</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-22T00:14:33</t>
+          <t>2026-06-22 05:49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49138508/austria-stefan-posch-play-argentina-broken-jaw</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Austria defender Stefan Posch will be available to play Monday against defending champion Argentina after sustaining a broken jaw in his team's win to</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5956178.html</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6.22竞足看点：挪威将面对非洲劲敌；阿根廷、奥地利阵容不整</t>
+          <t>队报：姆巴佩将出席法国对阵伊拉克的赛前发布会</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,12 +566,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-22 14:56</t>
+          <t>2026-06-22 01:34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5957008.html</t>
+          <t>https://www.dongqiudi.com/articles/5955831.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -589,68 +579,76 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentina vs Austria Prediction: World Cup 2026 Match Preview</t>
+          <t>Iraq coach jokes about France clash: 'I asked to play three goalkeepers'</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-21T09:34:56</t>
+          <t>2026-06-21T21:39:58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/argentina-vs-austria-prediction-world-cup-2026-match-preview/</t>
+          <t>https://www.espn.com/video/clip/_/id/49137854/asked-play-three-goalkeepers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Can Austria stop Lionel Messi making FIFA World Cup history and securing another win for Argentina? We look ahead to the game with our Argentina vs Au</t>
+          <t>Iraq coach jokes about France clash: 'I asked to play three goalkeepers'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>官方：埃及裁判阿明将执法世界杯阿根廷vs奥地利</t>
+          <t>France vs Iraq Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-19 20:46</t>
+          <t>2026-06-21T09:26:39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5949642.html</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/france-vs-iraq-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Can Kylian Mbappé make history as he joins France’s centurions club? Look ahead to this Group I clash at the 2026 FIFA World Cup with our France vs Ir</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>阿根廷vs奥地利：双方3分在手，战意层面可能会降低预期</t>
+          <t>德尚训话法国队不要轻敌：不要在心里把伊拉克当成一支弱队</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-21 06:33</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5956524&amp;from=tab_253</t>
+          <t>https://www.dongqiudi.com/articles/5953754.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -658,161 +656,717 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+          <t>队报：法国队战伊拉克可能遭遇雷暴天气</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 13</t>
+          <t>2026-06-21 04:17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953528.html</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Messi and Argentina ready to turn up the heat after fast World Cup start</t>
+          <t>RMC：伊拉克曾战平西班牙，德尚提醒法国队别轻敌</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 02</t>
+          <t>2026-06-20 20:04</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/22/lionel-messi-argentina-austria-world-cup</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It is the 40th anniversary of Diego Maradona’s exploits against England. The scene is set for Lionel Messi to imbue the date with fresh significance  </t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5952323.html</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Who will Cape Verde face in the next round?</t>
+          <t>France vs Iraq: predictions, best bets, odds and stats</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 00</t>
+          <t>1 hour ago</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/team/who-will-cape-verde-face-in-the-next-round</t>
+          <t>https://www.squawka.com/en/news/world-cup/france-vs-iraq-predictions-tips-22-06-26/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cape Verde are in dreamland so far in World Cup 2026.  They kicked things off with a draw against former champions Spain , and managed to score their </t>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>How do you stop Messi, Mbappe, Haaland and Kane?</t>
+          <t>‘Our performance until that stage had clearly made Kylian Mbappe angry, and suddenly you saw this explosion’ Frank Leboeuf on France’s epic World Cup 2022 final defeat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-22T08:10:21</t>
+          <t>Sun, 21 Jun 2026 15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cly8gpp39d0o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.fourfourtwo.com/person/player/our-performance-until-that-stage-had-clearly-made-kylian-mbappe-angry-and-suddenly-you-saw-this-explosion-frank-leboeuf-on-frances-epic-world-cup-2022-final-defeat</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Four of the most in-form strikers in world football will look to add to their red-hot starts to the World Cup this week  A World Cup is always that li</t>
+          <t>The 2022 World Cup final in Qatar was perhaps the most dramatic climax in the tournament’s storied history.  It was a match packed with momentum swing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-22 08:38</t>
+          <t>Sun, 21 Jun 2026 13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/article/5956424</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
-对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 09</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Quiz! Can you name every Frenchman to have played in a World Cup final?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 07</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/quiz/football-quiz-can-you-name-every-frenchman-to-have-played-in-a-world-cup-final</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLAY NOW You can play all FourFourTwo quizzes right HERE  France are back in action, and as one of the world's great superpowers, they've sprung into </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Squawka’s World Cup AI Predictor: AI score predictions for Monday June 22 at the 2026 World Cup</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9 hours ago</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/squawkas-world-cup-ai-predictor-22-06/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Using data from previous tournaments and qualifying, we’ve tasked our model with creating some World Cup AI predictions with correct score picks on ev</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>How do you stop Messi, Mbappe, Haaland and Kane?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-22T08:10:21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cly8gpp39d0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Four of the most in-form strikers in world football will look to add to their red-hot starts to the World Cup this week  A World Cup is always that li</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>官方：挪威vs伊拉克创97%收视率 是21世纪挪威世界杯赛事第2高</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-22 16:43:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38f548707e8native.htm</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6月22日世界杯看点：梅西雕像遭吐槽 阿根廷法国再登场</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:21:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e1f74a97anative.htm</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Slick Spain shine as Sharks shock the Celeste</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
+Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:21:55</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/norway-vs-senegal-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>After getting off to contrasting starts in their respective FIFA World Cup openers, Norway and Senegal will meet in New York in what is sure to be a h</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Argentina and France among quartet eyeing knockout stage</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
+Argentina m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>世界杯成移民球员最大舞台，99名法国出生者将为他国出战</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-21 18:02</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954863.html</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>伊拉克VS挪威这是哈兰德的第一次世界杯，如果梅开...</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-21 16:59</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5940517.html</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OptaJean：勒纳尔成法国第二位在世界杯执教3支国家队的教练</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:23</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954280.html</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mbappe and Olise hint at a partnership for the ages</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-20T18:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/kylian-mbappe-michael-olise-france-analysis</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kylian Mbappe and Michael Olise combined to thrilling effect as France opened their campaign with a 3-1 triumph over Senegal, offering a glimpse of a </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>The Four Major Storylines Fueling France’s World Cup 2026 Campaign</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-19T09:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/the-four-major-storylines-fueling-frances-world-cup-2026-campaign</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>From Mbappé’s off-pitch drama to Deschamps’ potential last dance, France arrive at the 2026 World Cup as favorites with plenty of storylines beyond th</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal: predictions, best bets, odds and stats</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/norway-vs-senegal-predictions-tips-23-06-26/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Iraq at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/iraq-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>A team profile of Iraq (Lions of Mesopotamia), back at the FIFA World Cup after 40 years: 58th in the FIFA ranking, 2nd appearance, Graham Arnold's ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>德尚：登贝莱需更加释放自我，相信他将在世界杯中发挥出色</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:22:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e0e6eadbcnative.htm</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>巴黎人报专栏：巴尔科拉or杜埃？德尚幸福的烦恼</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:53</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5957002.html</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>巴黎人报专栏：27岁的百场先生姆巴佩，永不停步</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:42</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956979.html</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>姆巴佩新闻发布会：我和奥利塞有默契；世界杯冠军最重要</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:30</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956504.html</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>武磊：感觉日本队每一个位置都没有短板，整体非常强大</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:32</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956412</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026美加墨世界杯小组赛第2轮角逐，日本队4-0大胜突尼斯队。上海海港球员武磊在连线节目中表示：“感觉日本队每一个位置都没有短板，整体非常强大。”
+武磊说道：“我觉得现在日本队整体非常强大，每一个位置感觉都比较平均，好像没有哪一个位置稍弱一点。就像刚才说的，前锋位置上，不只是一个得分点，有很多得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>朗尼克：如果亚马尔保持健康脚踏实地，他可能达到梅西的水平</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>2026-06-22 07:41</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956344</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>奥地利队主帅朗尼克在他们对阵阿根廷的赛前新闻发布会上表示，如果亚马尔能保持健康并脚踏实地，有可能达到梅西的水平。
 在被问到世界杯淘汰赛是否可能碰上西班牙时，朗尼克表示路易斯-德拉富恩特执教的球队“不是任何人都想面对的对手”。
@@ -820,960 +1374,256 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>萨比策：如果我们发挥最佳水平，对阿根廷是有机会赢球的</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-06-22 06:51</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/article/5956274</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6月21日，在对阵阿根廷的赛前新闻发布会，奥地利球员萨比策接受了采访。
-萨比策： 感觉很好，但我们整体是比较冷静的。我们非常享受作为一支球队在这里的每一天。
-在世界杯开始前我们就说过，我们想要创造属于自己的历史。
-第一场比赛赢下来之后，我们已经走在正确的道路上。现在我们可以继续书写这个故事。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>朗尼克：曼联的经历没有影响我的执教方式；阿根廷不只是梅西</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-06-22 06:45</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/article/5956250</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>6月21日，在对阵阿根廷的赛前新闻发布会，奥地利主帅朗尼克接受了采访。
-是的，当然，明天对我们来说是一场非常重要的比赛，也是一个巨大的机会。比赛条件非常好，球场条件也非常适合踢出一场高水平比赛。
-我们来到这里就是为了赢球，我们的目标就是赢下这场比赛。因此我们既有非常强烈的期待和兴奋，也有一定的紧</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Slick Spain shine as Sharks shock the Celeste</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-06-21T22:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
-Spain</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>goal_pw</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-06-21T17:04:43</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
-The 2026 FIFA World Cup has completely tak</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Youngest goalscorers in World Cup history</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-06-21T17:00:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/youngest-goalscorers-all-time</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">See a ranked list of the youngest all-time goalscorers in the FIFA World Cup.
-1st) Pele – 17 years &amp; 239 days
-2nd) Manuel Rosas – 18 years &amp; 93 days
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>goal_pw</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-06-21T16:35:30</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
-The 2026 FIFA World Cup has completely ta</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>goal_pw</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-06-21T16:11:53</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
-The 2026 FIFA World Cup has completely tak</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>The World Cup records that look set to be broken</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-06-21T13:55:05</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Dutch royals enjoy two big results in one World Cup day</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-06-21T09:45:57</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/c4gydq973nqo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">King Willem-Alexander celebrated with Curacao's players after they secured their first World Cup point  Two nations, four points, one crazy World Cup </t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>France vs Iraq Prediction: World Cup 2026 Match Preview</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-06-21T09:26:39</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/france-vs-iraq-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Can Kylian Mbappé make history as he joins France’s centurions club? Look ahead to this Group I clash at the 2026 FIFA World Cup with our France vs Ir</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Jordan vs Algeria Prediction: World Cup 2026 Match Preview</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-06-21T09:10:33</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/jordan-vs-algeria-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Who will get their first points in Group J of the 2026 World Cup ? We look ahead to Tuesday’s clash in San Francisco with our Jordan vs Algeria predic</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Argentina and France among quartet eyeing knockout stage</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-06-21T09:00:00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
-Argentina m</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Aimar: Messi has made us expect the unexpected</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-06-21T03:30:00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/pablo-aimar-messi</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Lionel Scaloni’s assistant on the Argentina bench discusses his relationship with the captain and La Albiceleste’s recent success.
-At the age of 12 o</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>官方：阿根廷裁判法尔孔将执法世界杯捷克vs墨西哥</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-06-21 20:50</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955283.html</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>官方：阿根廷裁判特略将执法世界杯南非vs韩国</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-06-21 20:43</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955267.html</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-06-20T23:46:26</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>FIFA World Cup Hat-Tricks: The Facts</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-06-19T00:28:32</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/world-cup-hat-tricks-fifa/</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>There have been 56 hat-tricks scored in men’s FIFA World Cup finals tournaments. We give a rundown of the best facts about World Cup hat-tricks, as we</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Golden Boot: World Cup 2026 top goalscorers</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Thu, 18 Jun 2026 08</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/golden-boot-world-cup-2026-top-goalscorers-winner</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Who is winning the battle to be top scorer at the World Cup? Live and updated throughout the tournament  All-time World Cup goalscorers  The Golden Bo</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Is Lamine Yamal the youngest player to have ever scored at the World Cup?</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>fourfourtwo</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 16</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://www.fourfourtwo.com/person/is-lamine-yamal-the-youngest-player-to-have-ever-scored-at-the-world-cup</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Lamine Yamal bagged his first-ever World Cup goal against Saudi Arabia, making him one of the youngest scorers in the competition’s history.  Spain we</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>‘Our performance until that stage had clearly made Kylian Mbappe angry, and suddenly you saw this explosion’ Frank Leboeuf on France’s epic World Cup 2022 final defeat</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>fourfourtwo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 15</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.fourfourtwo.com/person/player/our-performance-until-that-stage-had-clearly-made-kylian-mbappe-angry-and-suddenly-you-saw-this-explosion-frank-leboeuf-on-frances-epic-world-cup-2022-final-defeat</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>The 2022 World Cup final in Qatar was perhaps the most dramatic climax in the tournament’s storied history.  It was a match packed with momentum swing</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Room shuts door as Curaçao claim historic first World Cup point against Ecuador</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 02</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/curacao-ecuador-world-cup-group-e-match-report</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>It is doubtful whether many Ecuador supporters – or many others for that matter – had ever heard the name Eloy Room before this match. They will never</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Cape Verde at the World Cup: African nation have gained the hearts of the world as everyone's second team after brave draw with Uruguay</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>skysports</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Mon, 22 Jun 2026 07</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://www.skysports.com/football/news/12040/13556552/cape-verde-at-the-world-cup-african-nation-have-gained-the-hearts-of-the-world-as-everyones-second-team-after-brave-draw-with-uruguay</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Cape Verde claimed another point at the World Cup to stay unbeaten on their tournament debut; the African nation of 500,000 people showed bravery agai</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>‘If you love football, you love that Messi won a World Cup’ Alexia Putellas’ journey from teenage fan to sharing the spotlight with fellow Barcelona legend</t>
+          <t>姆巴佩：世界杯射手王？应该问梅西，我一直知道他会继续进球</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 04</t>
+          <t>2026-06-22 05:20</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/competition/if-you-love-football-you-love-that-messi-won-a-world-cup-alexia-putellas-journey-from-teenage-fan-to-sharing-the-spotlight-with-fellow-barcelona-legend</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Alexia Putellas has lived a football journey that once seemed impossible to the teenager that met Lionel Messi at Barcelona 14 years ago.  The Barcelo</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5956141.html</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Past and present World Cups collide as Beiranvand first gives Iran inspiration, then hope</t>
+          <t>姆巴佩：锋线三个位置我都能踢；数据无法体现登贝莱的作用</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 02</t>
+          <t>2026-06-22 05:05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-iran-goalkeeper-alireza-beiranvand</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The goalkeeper’s 59th-minute save left mouths agape but it’s not the first time he has created an indelible moment for the team  As they prepared for </t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5956081.html</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>World Cup 2026: Can Lionel Messi and Cristiano Ronaldo finally meet on biggest stage?</t>
+          <t>伊拉克主帅打趣：怎么防姆巴佩？我打算问问能不能上三个门将</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-06-22T06:43:30</t>
+          <t>2026-06-22 03:58</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48972466/world-cup-2026-lionel-messi-cristiano-ronaldo-showdown-knockouts-argentina-portugal</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>In a sixth World Cup for Lionel Messi and Cristiano Ronaldo, could the pair finally face each other in the tournament?</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5956032.html</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Salah's World Cup pain ends as he fires Egypt to historic win</t>
+          <t>RMC：姆巴佩的终极挑战是走进法国人的心里</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-06-22T04:23:40</t>
+          <t>2026-06-21 22:47</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c17yn5y977yo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Salah scores to help Egypt to first World Cup win  Mohamed Salah's - and Egypt's - World Cup wait is finally over.  The Egyptian King's match-winning </t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955495.html</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>De la Fuente: Spain are a family</t>
+          <t>世界杯首轮速度榜：澳大利亚后卫力压哈兰德居首，姆巴佩第9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-06-21T20:00:00</t>
+          <t>2026-06-21 09:10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/luis-de-la-fuente-spain-father-figure</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Spain coach Luis de la Fuente was like a proud papa watching his side take down Saudi Arabia on his 65th birthday.
-Luis de la Fuente turned 65 during</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5954018.html</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lamine Yamal shows why this could be his World Cup</t>
+          <t>队报：德尚或让迪涅、科内以及巴尔科拉首发出战伊拉克</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-06-21T19:27:01</t>
+          <t>2026-06-21 06:40</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cj0gy46d5vro?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'He's the main man!' - Rooney on Lamine Yamal  Lamine Yamal was the story before kick-off and is dominating conversation long after the final whistle </t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953739.html</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>The beauty of sharing your child's first World Cup</t>
+          <t>前队友：我曾担任过姆巴佩的队长，他偶像C罗且追求卓越</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-06-21T13:27:51</t>
-        </is>
-      </c>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cd957318ewdo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>There is nothing like the wonder of your first World Cup - the misty-eyed nostalgia of youth, summers that seemed to last forever, the gargantuan star</t>
-        </is>
-      </c>
+          <t>https://n.dongqiudi.com/webapp/feed.html?articleId=5957296&amp;_font=m&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Most FIFA World Cup Appearances by a Player</t>
+          <t>队报：登贝莱清楚近期的批评，他向队友保证会在球场上回应</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-06-20T19:39:34</t>
-        </is>
-      </c>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/most-world-cup-appearances-by-a-player/</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Here are the players who have combined longevity and excellence to record the most men’s FIFA World Cup appearances of all time.
-Lionel Messi: Argent</t>
-        </is>
-      </c>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5957172&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>The Oldest Players in World Cup History</t>
+          <t>England offer rare peek behind the curtain with no place to hide under Tuchel</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-06-20T19:09:14</t>
+          <t>Sun, 21 Jun 2026 00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/oldest-players-in-world-cup-history/</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/england-world-cup-training-intensity-peek-behind-curtain-thomas-tuchel</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Age is just a number for some footballers. Some even play the game on the grandest stage of all just before the end of their career. Here, we chart th</t>
+          <t xml:space="preserve">There was more insight at the World Cup training base than usual with intensity on the rise under Thomas Tuchel  T he tall hooded figure kept barking </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Six players climbing the FIFA Power Rankings</t>
+          <t>New Zealand World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-06-20T04:00:00</t>
+          <t>7 hours ago</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/six-players-climbing-fifa-power-rankings</t>
+          <t>https://www.squawka.com/en/news/world-cup/new-zealand-world-cup-2026-fixtures-squad-analysis/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">From Jonathan David and Matheus Cunha to Lucas Paqueta and Chris Richards, see which players have risen swiftly up the FIFA Power Rankings.
-Jonathan </t>
+          <t>This summer marks New Zealand’s third appearance at a World Cup . They went unbeaten in their most recent appearance in 2010, but three draws wasn’t e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Was Canada’s Win Over Qatar the Most One-Sided Game in World Cup History?</t>
+          <t>Senegal at the World Cup 2026: Team Guide — History, Style, Players &amp; Group I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-06-19T15:12:21</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/canada-win-over-qatar-one-sided-world-cup-2026/</t>
+          <t>https://kickoff.guide/blog/senegal-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>It was wave after wave after wave, only Qatar’s second match at the 2026 FIFA World Cup was anything but a day at the beach.
-World Cup co-hosts Canad</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Ecuador vs Curaçao Prediction: World Cup 2026 Match Preview</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-06-19T11:56:16</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/ecuador-vs-curacao-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Ecuador and Curaçao will be looking to keep their FIFA World Cup campaigns alive when they meet in Kansas City on Saturday.
-Curaçao will be hoping to</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Canada 6-0 Qatar Stats: Hat-Trick Hero David Inspires Co-Hosts’ Historic First World Cup Win</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-06-19T00:20:51</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/canada-vs-qatar-stats-world-cup-2026-live/</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Co-hosts Canada put on a show in front of their fans in Vancouver, firing six goals past a nine-man Qatar to secure a 6-0 win; the biggest FIFA World </t>
+          <t>A team profile of Senegal (Lions of Teranga) at the FIFA World Cup 2026: 14th in the FIFA ranking, 4th appearance, best result the quarter-finals in 2</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1826,82 +1676,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>伊拉克主帅：能和法国队交手是荣幸，也是我们展现实力的机会</t>
+          <t>Is Lionel Messi injured for Argentina vs Austria? World Cup star’s fitness latest</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-22 06:53</t>
+          <t>Mon, 22 Jun 2026 09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/article/5956272</t>
+          <t>https://www.fourfourtwo.com/person/player/is-lionel-messi-injured-for-argentina-vs-austria-world-cup-stars-fitness-latest</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>伊拉克将在世界杯小组赛第二场对阵法国，主帅阿诺德赛前接受了拜因体育的采访。
-对伊拉克队来说，这是一段非常美妙的经历。能够与法国队这样的球队交手，是一种荣幸。我之前也公开表示过，我非常享受这一切。无论是对阵挪威，还是接下来的比赛，都是如此。我从中收获了很多快乐。
-会的。为了争取最好的结果，我们必须</t>
+          <t xml:space="preserve">Lionel Messi has already caused a stir at World Cup 2026.  He needed just 76 minutes of this summer’s tournament to complete a hat-trick of finishes, </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>法媒：楚阿梅尼缺席法国战伊拉克前最后一练，预计不会首发</t>
+          <t>Argentina vs Austria preview: World Cup Group J at AT&amp;T Stadium</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:49</t>
+          <t>2026-06-22T08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956178.html</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>https://www.sofascore.com/news/argentina-vs-austria-preview-world-cup-group-j-at-att-stadium</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Argentina face Austria in World Cup Group J at AT&amp;T Stadium. We break down form, trends, projected lineups, odds, and the key Sofascore Rating leaders</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>队报：姆巴佩将出席法国对阵伊拉克的赛前发布会</t>
+          <t>Scaloni and Argentina prepare for Austria</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-22 01:34</t>
+          <t>2026-06-22T03:20:34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955831.html</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>https://www.espn.com/video/clip/_/id/49140889/scaloni-argentina-prepare-austria</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Lizzy Becherano analyzes Argentina's upcoming match against Austria in Dallas.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Iraq coach jokes about France clash: 'I asked to play three goalkeepers'</t>
+          <t>Austria's Stefan Posch will play vs. Argentina despite broken jaw</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1911,74 +1767,74 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-21T21:39:58</t>
+          <t>2026-06-22T00:14:33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49137854/asked-play-three-goalkeepers</t>
+          <t>https://www.espn.com/soccer/story/_/id/49138508/austria-stefan-posch-play-argentina-broken-jaw</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Iraq coach jokes about France clash: 'I asked to play three goalkeepers'</t>
+          <t>Austria defender Stefan Posch will be available to play Monday against defending champion Argentina after sustaining a broken jaw in his team's win to</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France vs Iraq Prediction: World Cup 2026 Match Preview</t>
+          <t>6.22竞足看点：挪威将面对非洲劲敌；阿根廷、奥地利阵容不整</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-21T09:26:39</t>
+          <t>2026-06-22 14:56</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/france-vs-iraq-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Can Kylian Mbappé make history as he joins France’s centurions club? Look ahead to this Group I clash at the 2026 FIFA World Cup with our France vs Ir</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5957008.html</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>德尚训话法国队不要轻敌：不要在心里把伊拉克当成一支弱队</t>
+          <t>Argentina vs Austria Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-21 06:33</t>
+          <t>2026-06-21T09:34:56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953754.html</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/argentina-vs-austria-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Can Austria stop Lionel Messi making FIFA World Cup history and securing another win for Argentina? We look ahead to the game with our Argentina vs Au</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>队报：法国队战伊拉克可能遭遇雷暴天气</t>
+          <t>官方：埃及裁判阿明将执法世界杯阿根廷vs奥地利</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1988,12 +1844,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-21 04:17</t>
+          <t>2026-06-19 20:46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953528.html</t>
+          <t>https://www.dongqiudi.com/articles/5949642.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -2001,52 +1857,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RMC：伊拉克曾战平西班牙，德尚提醒法国队别轻敌</t>
+          <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-20 20:04</t>
+          <t>1 hour ago</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5952323.html</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>‘Our performance until that stage had clearly made Kylian Mbappe angry, and suddenly you saw this explosion’ Frank Leboeuf on France’s epic World Cup 2022 final defeat</t>
+          <t>阿根廷vs奥地利：双方3分在手，战意层面可能会降低预期</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 15</t>
-        </is>
-      </c>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/person/player/our-performance-until-that-stage-had-clearly-made-kylian-mbappe-angry-and-suddenly-you-saw-this-explosion-frank-leboeuf-on-frances-epic-world-cup-2022-final-defeat</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>The 2022 World Cup final in Qatar was perhaps the most dramatic climax in the tournament’s storied history.  It was a match packed with momentum swing</t>
-        </is>
-      </c>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5956524&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2078,7 +1934,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
+          <t>Messi and Argentina ready to turn up the heat after fast World Cup start</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2088,24 +1944,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 09</t>
+          <t>Mon, 22 Jun 2026 02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
+          <t>https://www.theguardian.com/football/2026/jun/22/lionel-messi-argentina-austria-world-cup</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
+          <t xml:space="preserve">It is the 40th anniversary of Diego Maradona’s exploits against England. The scene is set for Lionel Messi to imbue the date with fresh significance  </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quiz! Can you name every Frenchman to have played in a World Cup final?</t>
+          <t>Who will Cape Verde face in the next round?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2115,399 +1971,170 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07</t>
+          <t>Mon, 22 Jun 2026 00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/quiz/football-quiz-can-you-name-every-frenchman-to-have-played-in-a-world-cup-final</t>
+          <t>https://www.fourfourtwo.com/team/who-will-cape-verde-face-in-the-next-round</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAY NOW You can play all FourFourTwo quizzes right HERE  France are back in action, and as one of the world's great superpowers, they've sprung into </t>
+          <t xml:space="preserve">Cape Verde are in dreamland so far in World Cup 2026.  They kicked things off with a draw against former champions Spain , and managed to score their </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>How do you stop Messi, Mbappe, Haaland and Kane?</t>
+          <t>Squawka’s World Cup AI Predictor: AI score predictions for Monday June 22 at the 2026 World Cup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-22T08:10:21</t>
+          <t>9 hours ago</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cly8gpp39d0o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.squawka.com/en/news/world-cup/squawkas-world-cup-ai-predictor-22-06/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Four of the most in-form strikers in world football will look to add to their red-hot starts to the World Cup this week  A World Cup is always that li</t>
+          <t>Using data from previous tournaments and qualifying, we’ve tasked our model with creating some World Cup AI predictions with correct score picks on ev</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Slick Spain shine as Sharks shock the Celeste</t>
+          <t>How do you stop Messi, Mbappe, Haaland and Kane?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-21T22:00:00</t>
+          <t>2026-06-22T08:10:21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
+          <t>https://www.bbc.com/sport/football/articles/cly8gpp39d0o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
-Spain</t>
+          <t>Four of the most in-form strikers in world football will look to add to their red-hot starts to the World Cup this week  A World Cup is always that li</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>The World Cup records that look set to be broken</t>
+          <t>撞上大魔王？32强最新预测：佛得角碰阿根廷！埃及头名力压比利时</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>zhibo8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-21T13:55:05</t>
+          <t>2026-06-22 16:29:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
-        </is>
-      </c>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38f16371d91native.htm</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Norway vs Senegal Prediction: World Cup 2026 Match Preview</t>
+          <t>6月22日世界杯看点：梅西雕像遭吐槽 阿根廷法国再登场</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>zhibo8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-21T09:21:55</t>
+          <t>2026-06-22 15:21:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/norway-vs-senegal-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>After getting off to contrasting starts in their respective FIFA World Cup openers, Norway and Senegal will meet in New York in what is sure to be a h</t>
-        </is>
-      </c>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e1f74a97anative.htm</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentina and France among quartet eyeing knockout stage</t>
+          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>dongqiudi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-21T09:00:00</t>
+          <t>2026-06-22 08:38</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
+          <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
-Argentina m</t>
+          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
+对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>世界杯成移民球员最大舞台，99名法国出生者将为他国出战</t>
+          <t>朗尼克：如果亚马尔保持健康脚踏实地，他可能达到梅西的水平</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>dongqiudi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-21 18:02</t>
+          <t>2026-06-22 07:41</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954863.html</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>伊拉克VS挪威这是哈兰德的第一次世界杯，如果梅开...</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-06-21 16:59</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5940517.html</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>OptaJean：勒纳尔成法国第二位在世界杯执教3支国家队的教练</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-06-21 11:23</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5954280.html</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Mbappe and Olise hint at a partnership for the ages</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-06-20T18:00:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/kylian-mbappe-michael-olise-france-analysis</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kylian Mbappe and Michael Olise combined to thrilling effect as France opened their campaign with a 3-1 triumph over Senegal, offering a glimpse of a </t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>The Four Major Storylines Fueling France’s World Cup 2026 Campaign</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-06-19T09:30:00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/the-four-major-storylines-fueling-frances-world-cup-2026-campaign</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>From Mbappé’s off-pitch drama to Deschamps’ potential last dance, France arrive at the 2026 World Cup as favorites with plenty of storylines beyond th</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>巴黎人报专栏：巴尔科拉or杜埃？德尚幸福的烦恼</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-06-22 14:53</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5957002.html</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>巴黎人报专栏：27岁的百场先生姆巴佩，永不停步</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-06-22 14:42</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5956979.html</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>姆巴佩新闻发布会：我和奥利塞有默契；世界杯冠军最重要</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-06-22 09:30</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5956504.html</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>武磊：感觉日本队每一个位置都没有短板，整体非常强大</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-06-22 08:32</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/article/5956412</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026美加墨世界杯小组赛第2轮角逐，日本队4-0大胜突尼斯队。上海海港球员武磊在连线节目中表示：“感觉日本队每一个位置都没有短板，整体非常强大。”
-武磊说道：“我觉得现在日本队整体非常强大，每一个位置感觉都比较平均，好像没有哪一个位置稍弱一点。就像刚才说的，前锋位置上，不只是一个得分点，有很多得分</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>朗尼克：如果亚马尔保持健康脚踏实地，他可能达到梅西的水平</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:41</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
           <t>https://www.dongqiudi.com/article/5956344</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>奥地利队主帅朗尼克在他们对阵阿根廷的赛前新闻发布会上表示，如果亚马尔能保持健康并脚踏实地，有可能达到梅西的水平。
 在被问到世界杯淘汰赛是否可能碰上西班牙时，朗尼克表示路易斯-德拉富恩特执教的球队“不是任何人都想面对的对手”。
@@ -2515,102 +2142,376 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>萨比策：如果我们发挥最佳水平，对阿根廷是有机会赢球的</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:51</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956274</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6月21日，在对阵阿根廷的赛前新闻发布会，奥地利球员萨比策接受了采访。
+萨比策： 感觉很好，但我们整体是比较冷静的。我们非常享受作为一支球队在这里的每一天。
+在世界杯开始前我们就说过，我们想要创造属于自己的历史。
+第一场比赛赢下来之后，我们已经走在正确的道路上。现在我们可以继续书写这个故事。
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>朗尼克：曼联的经历没有影响我的执教方式；阿根廷不只是梅西</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:45</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956250</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6月21日，在对阵阿根廷的赛前新闻发布会，奥地利主帅朗尼克接受了采访。
+是的，当然，明天对我们来说是一场非常重要的比赛，也是一个巨大的机会。比赛条件非常好，球场条件也非常适合踢出一场高水平比赛。
+我们来到这里就是为了赢球，我们的目标就是赢下这场比赛。因此我们既有非常强烈的期待和兴奋，也有一定的紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Slick Spain shine as Sharks shock the Celeste</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
+Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-21T17:04:43</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Youngest goalscorers in World Cup history</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-21T17:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/youngest-goalscorers-all-time</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">See a ranked list of the youngest all-time goalscorers in the FIFA World Cup.
+1st) Pele – 17 years &amp; 239 days
+2nd) Manuel Rosas – 18 years &amp; 93 days
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:35:30</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
+The 2026 FIFA World Cup has completely ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:11:53</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dutch royals enjoy two big results in one World Cup day</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:45:57</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c4gydq973nqo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">King Willem-Alexander celebrated with Curacao's players after they secured their first World Cup point  Two nations, four points, one crazy World Cup </t>
+        </is>
+      </c>
+    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>姆巴佩：世界杯射手王？应该问梅西，我一直知道他会继续进球</t>
+          <t>France vs Iraq Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-22 05:20</t>
+          <t>2026-06-21T09:26:39</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956141.html</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/france-vs-iraq-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Can Kylian Mbappé make history as he joins France’s centurions club? Look ahead to this Group I clash at the 2026 FIFA World Cup with our France vs Ir</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>姆巴佩：锋线三个位置我都能踢；数据无法体现登贝莱的作用</t>
+          <t>Jordan vs Algeria Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-22 05:05</t>
+          <t>2026-06-21T09:10:33</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956081.html</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/jordan-vs-algeria-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Who will get their first points in Group J of the 2026 World Cup ? We look ahead to Tuesday’s clash in San Francisco with our Jordan vs Algeria predic</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>伊拉克主帅打趣：怎么防姆巴佩？我打算问问能不能上三个门将</t>
+          <t>Argentina and France among quartet eyeing knockout stage</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-22 03:58</t>
+          <t>2026-06-21T09:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956032.html</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
+Argentina m</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RMC：姆巴佩的终极挑战是走进法国人的心里</t>
+          <t>Aimar: Messi has made us expect the unexpected</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-21 22:47</t>
+          <t>2026-06-21T03:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955495.html</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>https://www.fifa.com/en/articles/pablo-aimar-messi</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Lionel Scaloni’s assistant on the Argentina bench discusses his relationship with the captain and La Albiceleste’s recent success.
+At the age of 12 o</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>世界杯首轮速度榜：澳大利亚后卫力压哈兰德居首，姆巴佩第9</t>
+          <t>官方：阿根廷裁判法尔孔将执法世界杯捷克vs墨西哥</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2620,12 +2521,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-21 09:10</t>
+          <t>2026-06-21 20:50</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954018.html</t>
+          <t>https://www.dongqiudi.com/articles/5955283.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2633,7 +2534,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>队报：德尚或让迪涅、科内以及巴尔科拉首发出战伊拉克</t>
+          <t>官方：阿根廷裁判特略将执法世界杯南非vs韩国</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2643,12 +2544,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-21 06:40</t>
+          <t>2026-06-21 20:43</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953739.html</t>
+          <t>https://www.dongqiudi.com/articles/5955267.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2656,40 +2557,798 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>前队友：我曾担任过姆巴佩的队长，他偶像C罗且追求卓越</t>
+          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-20T23:46:26</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://n.dongqiudi.com/webapp/feed.html?articleId=5957296&amp;_font=m&amp;from=tab_253</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>队报：登贝莱清楚近期的批评，他向队友保证会在球场上回应</t>
+          <t>FIFA World Cup Hat-Tricks: The Facts</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-19T00:28:32</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5957172&amp;from=tab_253</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/world-cup-hat-tricks-fifa/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>There have been 56 hat-tricks scored in men’s FIFA World Cup finals tournaments. We give a rundown of the best facts about World Cup hat-tricks, as we</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jordan vs Algeria: predictions, best bets, odds and stats</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/jordan-vs-algeria-predictions-tips-23-06-26/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Austria at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/austria-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>A team profile of Austria, back at the FIFA World Cup after 28 years: 24th in the FIFA ranking, 8th appearance, Ralf Rangnick's tactics, players to wa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Argentina at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/argentina-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>A team profile of defending champions Argentina at the FIFA World Cup 2026: 3rd in the FIFA ranking, 19th appearance, three-time winners, Lionel Scalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Golden Boot: World Cup 2026 top goalscorers</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 08</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/golden-boot-world-cup-2026-top-goalscorers-winner</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Who is winning the battle to be top scorer at the World Cup? Live and updated throughout the tournament  All-time World Cup goalscorers  The Golden Bo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Is Lamine Yamal the youngest player to have ever scored at the World Cup?</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 16</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/is-lamine-yamal-the-youngest-player-to-have-ever-scored-at-the-world-cup</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Lamine Yamal bagged his first-ever World Cup goal against Saudi Arabia, making him one of the youngest scorers in the competition’s history.  Spain we</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>‘Our performance until that stage had clearly made Kylian Mbappe angry, and suddenly you saw this explosion’ Frank Leboeuf on France’s epic World Cup 2022 final defeat</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/our-performance-until-that-stage-had-clearly-made-kylian-mbappe-angry-and-suddenly-you-saw-this-explosion-frank-leboeuf-on-frances-epic-world-cup-2022-final-defeat</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>The 2022 World Cup final in Qatar was perhaps the most dramatic climax in the tournament’s storied history.  It was a match packed with momentum swing</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Room shuts door as Curaçao claim historic first World Cup point against Ecuador</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 02</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/curacao-ecuador-world-cup-group-e-match-report</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>It is doubtful whether many Ecuador supporters – or many others for that matter – had ever heard the name Eloy Room before this match. They will never</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cape Verde at the World Cup: African nation have gained the hearts of the world as everyone's second team after brave draw with Uruguay</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 07</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/news/12040/13556552/cape-verde-at-the-world-cup-african-nation-have-gained-the-hearts-of-the-world-as-everyones-second-team-after-brave-draw-with-uruguay</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Cape Verde claimed another point at the World Cup to stay unbeaten on their tournament debut; the African nation of 500,000 people showed bravery agai</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>‘If you love football, you love that Messi won a World Cup’ Alexia Putellas’ journey from teenage fan to sharing the spotlight with fellow Barcelona legend</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/if-you-love-football-you-love-that-messi-won-a-world-cup-alexia-putellas-journey-from-teenage-fan-to-sharing-the-spotlight-with-fellow-barcelona-legend</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Alexia Putellas has lived a football journey that once seemed impossible to the teenager that met Lionel Messi at Barcelona 14 years ago.  The Barcelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Past and present World Cups collide as Beiranvand first gives Iran inspiration, then hope</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 02</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-iran-goalkeeper-alireza-beiranvand</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The goalkeeper’s 59th-minute save left mouths agape but it’s not the first time he has created an indelible moment for the team  As they prepared for </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Can Lionel Messi and Cristiano Ronaldo finally meet on biggest stage?</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-06-22T06:43:30</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/48972466/world-cup-2026-lionel-messi-cristiano-ronaldo-showdown-knockouts-argentina-portugal</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>In a sixth World Cup for Lionel Messi and Cristiano Ronaldo, could the pair finally face each other in the tournament?</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Salah's World Cup pain ends as he fires Egypt to historic win</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-06-22T04:23:40</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c17yn5y977yo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salah scores to help Egypt to first World Cup win  Mohamed Salah's - and Egypt's - World Cup wait is finally over.  The Egyptian King's match-winning </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>De la Fuente: Spain are a family</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-06-21T20:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/luis-de-la-fuente-spain-father-figure</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Spain coach Luis de la Fuente was like a proud papa watching his side take down Saudi Arabia on his 65th birthday.
+Luis de la Fuente turned 65 during</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Lamine Yamal shows why this could be his World Cup</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-06-21T19:27:01</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cj0gy46d5vro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'He's the main man!' - Rooney on Lamine Yamal  Lamine Yamal was the story before kick-off and is dominating conversation long after the final whistle </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The beauty of sharing your child's first World Cup</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:27:51</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cd957318ewdo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>There is nothing like the wonder of your first World Cup - the misty-eyed nostalgia of youth, summers that seemed to last forever, the gargantuan star</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Most FIFA World Cup Appearances by a Player</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-06-20T19:39:34</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/most-world-cup-appearances-by-a-player/</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Here are the players who have combined longevity and excellence to record the most men’s FIFA World Cup appearances of all time.
+Lionel Messi: Argent</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>The Oldest Players in World Cup History</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-06-20T19:09:14</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/oldest-players-in-world-cup-history/</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Age is just a number for some footballers. Some even play the game on the grandest stage of all just before the end of their career. Here, we chart th</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Six players climbing the FIFA Power Rankings</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:00:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/six-players-climbing-fifa-power-rankings</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Jonathan David and Matheus Cunha to Lucas Paqueta and Chris Richards, see which players have risen swiftly up the FIFA Power Rankings.
+Jonathan </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Was Canada’s Win Over Qatar the Most One-Sided Game in World Cup History?</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-19T15:12:21</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/canada-win-over-qatar-one-sided-world-cup-2026/</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>It was wave after wave after wave, only Qatar’s second match at the 2026 FIFA World Cup was anything but a day at the beach.
+World Cup co-hosts Canad</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ecuador vs Curaçao Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-19T11:56:16</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/ecuador-vs-curacao-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ecuador and Curaçao will be looking to keep their FIFA World Cup campaigns alive when they meet in Kansas City on Saturday.
+Curaçao will be hoping to</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Canada 6-0 Qatar Stats: Hat-Trick Hero David Inspires Co-Hosts’ Historic First World Cup Win</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-19T00:20:51</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/canada-vs-qatar-stats-world-cup-2026-live/</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Co-hosts Canada put on a show in front of their fans in Vancouver, firing six goals past a nine-man Qatar to secure a 6-0 win; the biggest FIFA World </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Tunisia World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/tunisia-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Tunisia have never reached the knockout stages of the World Cup and will miss out yet again. They’ve bowed out at the group stage in each of their sev</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>J组形势：阿根廷赢球即出线！若同时约旦不胜，阿根廷将锁定头名</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:50:15</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a37a66c0e83fnative.htm</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>世体：约旦对阵阿尔及利亚，J组生死战</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:33</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956962.html</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>12 hours ago</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jordan at the World Cup 2026: Team Guide — History, Style, Players &amp; Group J</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/jordan-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>A team profile of Jordan (Al-Nashama), who reached a first-ever FIFA World Cup: 63rd in the FIFA ranking, 2023 Asian Cup runners-up, Jamal Sellami's t</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Algeria at the World Cup 2026: Team Guide — History, Style, Players &amp; Group J</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/algeria-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>A team profile of Algeria (Desert Foxes), back at the FIFA World Cup after 12 years: 35th in the FIFA ranking, 5th appearance, best result Round of 16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2702,7 +3361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2813,122 +3472,203 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>挪威vs塞内加尔：北欧海盗强势出击，但数据层面给不出支持</t>
+          <t>Norway vs Senegal: predictions, best bets, odds and stats</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5956551&amp;from=tab_253</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>https://www.squawka.com/en/news/world-cup/norway-vs-senegal-predictions-tips-23-06-26/</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>How do you stop Messi, Mbappe, Haaland and Kane?</t>
+          <t>挪威vs塞内加尔：北欧海盗强势出击，但数据层面给不出支持</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-22T08:10:21</t>
-        </is>
-      </c>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cly8gpp39d0o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Four of the most in-form strikers in world football will look to add to their red-hot starts to the World Cup this week  A World Cup is always that li</t>
-        </is>
-      </c>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5956551&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6.22竞足看点：挪威将面对非洲劲敌；阿根廷、奥地利阵容不整</t>
+          <t>Squawka’s World Cup AI Predictor: AI score predictions for Monday June 22 at the 2026 World Cup</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-22 14:56</t>
+          <t>9 hours ago</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5957008.html</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>https://www.squawka.com/en/news/world-cup/squawkas-world-cup-ai-predictor-22-06/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Using data from previous tournaments and qualifying, we’ve tasked our model with creating some World Cup AI predictions with correct score picks on ev</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>How do you stop Messi, Mbappe, Haaland and Kane?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-22T08:10:21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cly8gpp39d0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Four of the most in-form strikers in world football will look to add to their red-hot starts to the World Cup this week  A World Cup is always that li</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>官方：挪威vs伊拉克创97%收视率 是21世纪挪威世界杯赛事第2高</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-22 16:43:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38f548707e8native.htm</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6.22竞足看点：挪威将面对非洲劲敌；阿根廷、奥地利阵容不整</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:56</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5957008.html</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>塞内加尔主帅：哈兰德非常出色，但我们也有非常优秀的后卫</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-06-22 07:13</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956281</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>塞内加尔将在世界杯小组赛第二场对阵挪威，主帅蒂奥赛前接受了拜因体育的采访。
 不会。在我的执教理念中，我们从来不会只针对某一名球员制定比赛计划。我们知道哈兰德是一名非常出色的前锋，也是世界上最优秀的前锋之一。他只要获得半次机会，就有能力把球送进球门。与此同时，我们也拥有非常优秀的后卫，他们习惯于面对</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>塞内加尔主帅：不会专门制定针对哈兰德的战术；后勤问题未影响球队</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2026-06-22 06:07</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956182</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>6月21日，在即将对阵挪威队赛前，塞内加尔主帅蒂奥接受了采访。
 是的，距离比赛已经只剩大约24小时，我们将迎来与挪威队的对决。这是一场非常困难的比赛，我们对此非常清楚。我们已经做了充分准备，对对手进行了非常细致的分析，包括他们的比赛录像、战术特点以及他们的优势和强项。
@@ -2936,208 +3676,143 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>塞内加尔主帅：能执教自己的祖国参加世界杯是一种莫大的荣耀</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>dongqiudi_team</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2026-06-22 01:51</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/articles/5955868.html</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Slick Spain shine as Sharks shock the Celeste</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-06-21T22:00:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
 Spain</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>The World Cup records that look set to be broken</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2026-06-21T13:55:05</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>France vs Iraq Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2026-06-21T09:26:39</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/france-vs-iraq-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Can Kylian Mbappé make history as he joins France’s centurions club? Look ahead to this Group I clash at the 2026 FIFA World Cup with our France vs Ir</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Argentina and France among quartet eyeing knockout stage</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>2026-06-21T09:00:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
 Argentina m</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>伊拉克VS挪威这是哈兰德的第一次世界杯，如果梅开...</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-06-21 16:59</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5940517.html</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>据报道，塞内加尔世界杯训练营一片混乱……</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-06-20 22:24</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5952852.html</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>挪威首战平均观众130万，为本世纪挪威国内世界杯比赛第二高</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5957229&amp;from=tab_253</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>伊布：哈兰德球商很高，不像有些球员爱强行做超出能力的事情</t>
+          <t>伊拉克VS挪威这是哈兰德的第一次世界杯，如果梅开...</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3147,12 +3822,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-22 11:32</t>
+          <t>2026-06-21 16:59</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956713.html</t>
+          <t>https://www.dongqiudi.com/articles/5940517.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -3160,7 +3835,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>索尔巴肯：会在进攻端继续给哈兰德支持，厄德高训练状态不错</t>
+          <t>据报道，塞内加尔世界杯训练营一片混乱……</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3170,12 +3845,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12</t>
+          <t>2026-06-20 22:24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956529.html</t>
+          <t>https://www.dongqiudi.com/articles/5952852.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -3183,45 +3858,49 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>塞内加尔门将：哈兰德效率非常高，但足球是一项团队运动</t>
+          <t>France vs Iraq: predictions, best bets, odds and stats</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-22 06:13</t>
+          <t>1 hour ago</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956235.html</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>https://www.squawka.com/en/news/world-cup/france-vs-iraq-predictions-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>尼亚凯特：哈兰德是我交手次数最多的球员之一，见他像老熟人</t>
+          <t>挪威首战平均观众130万，为本世纪挪威国内世界杯比赛第二高</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-06-21 22:03</t>
-        </is>
-      </c>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955400.html</t>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5957229&amp;from=tab_253</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -3229,48 +3908,267 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>世界杯首轮速度榜：澳大利亚后卫力压哈兰德居首，姆巴佩第9</t>
+          <t>Norway at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-06-21 09:10</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954018.html</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>https://kickoff.guide/blog/norway-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>A team profile of Norway, back at the FIFA World Cup after 28 years: 32nd in the FIFA ranking, 4th appearance, Stale Solbakken's tactics, stars Erling</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Senegal at the World Cup 2026: Team Guide — History, Style, Players &amp; Group I</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/senegal-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>A team profile of Senegal (Lions of Teranga) at the FIFA World Cup 2026: 14th in the FIFA ranking, 4th appearance, best result the quarter-finals in 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>伊布：哈兰德球商很高，不像有些球员爱强行做超出能力的事情</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:32</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956713.html</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>索尔巴肯：会在进攻端继续给哈兰德支持，厄德高训练状态不错</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956529.html</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>塞内加尔门将：哈兰德效率非常高，但足球是一项团队运动</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:13</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956235.html</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>尼亚凯特：哈兰德是我交手次数最多的球员之一，见他像老熟人</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-21 22:03</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955400.html</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>世界杯首轮速度榜：澳大利亚后卫力压哈兰德居首，姆巴佩第9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:10</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954018.html</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>邮报盘点哈兰德奢侈品收藏：33万镑爱马仕包、28万豪华腕表</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>dongqiudi_team</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2026-06-21 09:01</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/articles/5954007.html</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>England offer rare peek behind the curtain with no place to hide under Tuchel</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/england-world-cup-training-intensity-peek-behind-curtain-thomas-tuchel</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">There was more insight at the World Cup training base than usual with intensity on the rise under Thomas Tuchel  T he tall hooded figure kept barking </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>New Zealand World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7 hours ago</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/new-zealand-world-cup-2026-fixtures-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>This summer marks New Zealand’s third appearance at a World Cup . They went unbeaten in their most recent appearance in 2010, but three draws wasn’t e</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mbappe and Olise hint at a partnership for the ages</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-20T18:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/kylian-mbappe-michael-olise-france-analysis</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kylian Mbappe and Michael Olise combined to thrilling effect as France opened their campaign with a 3-1 triumph over Senegal, offering a glimpse of a </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3283,7 +4181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3394,138 +4292,460 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Messi and Argentina ready to turn up the heat after fast World Cup start</t>
+          <t>Jordan vs Algeria: predictions, best bets, odds and stats</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 02</t>
+          <t>1 hour ago</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/22/lionel-messi-argentina-austria-world-cup</t>
+          <t>https://www.squawka.com/en/news/world-cup/jordan-vs-algeria-predictions-tips-23-06-26/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">It is the 40th anniversary of Diego Maradona’s exploits against England. The scene is set for Lionel Messi to imbue the date with fresh significance  </t>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Messi and Argentina ready to turn up the heat after fast World Cup start</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 02</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/lionel-messi-argentina-austria-world-cup</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is the 40th anniversary of Diego Maradona’s exploits against England. The scene is set for Lionel Messi to imbue the date with fresh significance  </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Squawka’s World Cup AI Predictor: AI score predictions for Monday June 22 at the 2026 World Cup</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9 hours ago</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/squawkas-world-cup-ai-predictor-22-06/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Using data from previous tournaments and qualifying, we’ve tasked our model with creating some World Cup AI predictions with correct score picks on ev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>不虚此行！新军佛得角、库拉索、约旦、乌兹均取得世界杯首球</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-06-22 06:32</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956261</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2026年美加墨世界杯扩军至48支球队，佛得角、库拉索、约旦、乌兹别克斯坦成为了本届世界杯的四支新军。在佛得角队取得历史性首球后，本届世界杯的四支新军都已经取得进球，其中佛得角和库拉索还实现了拿一分的目标。
 佛得角世界杯首秀0-0逼平西班牙，就已经足够令人震惊，他们又在与乌拉圭的比赛中由凯文-皮纳</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Slick Spain shine as Sharks shock the Celeste</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-06-21T22:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
 Spain</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Argentina vs Austria Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-06-21T09:34:56</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/argentina-vs-austria-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Can Austria stop Lionel Messi making FIFA World Cup history and securing another win for Argentina? We look ahead to the game with our Argentina vs Au</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Argentina and France among quartet eyeing knockout stage</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-06-21T09:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
 Argentina m</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jordan at the World Cup 2026: Team Guide — History, Style, Players &amp; Group J</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/jordan-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>A team profile of Jordan (Al-Nashama), who reached a first-ever FIFA World Cup: 63rd in the FIFA ranking, 2023 Asian Cup runners-up, Jamal Sellami's t</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Algeria at the World Cup 2026: Team Guide — History, Style, Players &amp; Group J</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/algeria-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>A team profile of Algeria (Desert Foxes), back at the FIFA World Cup after 12 years: 35th in the FIFA ranking, 5th appearance, best result Round of 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Is Lionel Messi injured for Argentina vs Austria? World Cup star’s fitness latest</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 09</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/is-lionel-messi-injured-for-argentina-vs-austria-world-cup-stars-fitness-latest</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lionel Messi has already caused a stir at World Cup 2026.  He needed just 76 minutes of this summer’s tournament to complete a hat-trick of finishes, </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria preview: World Cup Group J at AT&amp;T Stadium</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-22T08:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/argentina-vs-austria-preview-world-cup-group-j-at-att-stadium</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Argentina face Austria in World Cup Group J at AT&amp;T Stadium. We break down form, trends, projected lineups, odds, and the key Sofascore Rating leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>J组形势：阿根廷赢球即出线！若同时约旦不胜，阿根廷将锁定头名</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:50:15</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a37a66c0e83fnative.htm</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:38</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956424</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
+对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>12 hours ago</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
         </is>
       </c>
     </row>
